--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_13-08-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_13-08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39BDFB79-AE5C-43EB-9DF0-D22BDD474A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E550C9D-1021-4CE6-A0D7-538114CBB163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31065" yWindow="1575" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30915" yWindow="2100" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -529,9 +529,6 @@
     <t>£58.97</t>
   </si>
   <si>
-    <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Max retries exceeded with url: /product/150mm-recticel-gp-insulation-board-2400x1200mm/ (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.onlineinsulation-sales.com', port=443) at 0x1b097a1b0d0&gt;, 'Connection to www.onlineinsulation-sales.com timed out. (connect timeout=None)'))</t>
-  </si>
-  <si>
     <t>£62.09</t>
   </si>
   <si>
@@ -812,6 +809,9 @@
   </si>
   <si>
     <t>£716.05</t>
+  </si>
+  <si>
+    <t>£57.75</t>
   </si>
 </sst>
 </file>
@@ -1306,7 +1306,7 @@
         <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G3" t="s">
         <v>36</v>
@@ -1327,10 +1327,10 @@
         <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O3" t="s">
         <v>41</v>
@@ -1362,7 +1362,7 @@
         <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G4" t="s">
         <v>47</v>
@@ -1374,7 +1374,7 @@
         <v>49</v>
       </c>
       <c r="J4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K4" t="s">
         <v>50</v>
@@ -1383,10 +1383,10 @@
         <v>26</v>
       </c>
       <c r="M4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="N4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O4" t="s">
         <v>51</v>
@@ -1418,7 +1418,7 @@
         <v>55</v>
       </c>
       <c r="F5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G5" t="s">
         <v>56</v>
@@ -1430,7 +1430,7 @@
         <v>58</v>
       </c>
       <c r="J5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K5" t="s">
         <v>59</v>
@@ -1442,7 +1442,7 @@
         <v>60</v>
       </c>
       <c r="N5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O5" t="s">
         <v>61</v>
@@ -1474,7 +1474,7 @@
         <v>66</v>
       </c>
       <c r="F6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G6" t="s">
         <v>67</v>
@@ -1498,7 +1498,7 @@
         <v>72</v>
       </c>
       <c r="N6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O6" t="s">
         <v>73</v>
@@ -1530,7 +1530,7 @@
         <v>77</v>
       </c>
       <c r="F7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G7" t="s">
         <v>78</v>
@@ -1586,7 +1586,7 @@
         <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G8" t="s">
         <v>89</v>
@@ -1598,7 +1598,7 @@
         <v>90</v>
       </c>
       <c r="J8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K8" t="s">
         <v>91</v>
@@ -1610,7 +1610,7 @@
         <v>92</v>
       </c>
       <c r="N8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O8" t="s">
         <v>93</v>
@@ -1642,7 +1642,7 @@
         <v>97</v>
       </c>
       <c r="F9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G9" t="s">
         <v>98</v>
@@ -1666,7 +1666,7 @@
         <v>103</v>
       </c>
       <c r="N9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O9" t="s">
         <v>104</v>
@@ -1698,7 +1698,7 @@
         <v>109</v>
       </c>
       <c r="F10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G10" t="s">
         <v>110</v>
@@ -1754,7 +1754,7 @@
         <v>109</v>
       </c>
       <c r="F11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G11" t="s">
         <v>118</v>
@@ -1778,7 +1778,7 @@
         <v>123</v>
       </c>
       <c r="N11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O11" t="s">
         <v>124</v>
@@ -1810,7 +1810,7 @@
         <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G12" t="s">
         <v>130</v>
@@ -1831,7 +1831,7 @@
         <v>26</v>
       </c>
       <c r="M12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="N12" t="s">
         <v>30</v>
@@ -1866,7 +1866,7 @@
         <v>135</v>
       </c>
       <c r="F13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G13" t="s">
         <v>136</v>
@@ -1890,7 +1890,7 @@
         <v>141</v>
       </c>
       <c r="N13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O13" t="s">
         <v>142</v>
@@ -1922,7 +1922,7 @@
         <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G14" t="s">
         <v>147</v>
@@ -1946,7 +1946,7 @@
         <v>152</v>
       </c>
       <c r="N14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O14" t="s">
         <v>153</v>
@@ -1978,7 +1978,7 @@
         <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G15" t="s">
         <v>157</v>
@@ -2002,7 +2002,7 @@
         <v>162</v>
       </c>
       <c r="N15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O15" t="s">
         <v>163</v>
@@ -2034,57 +2034,57 @@
         <v>167</v>
       </c>
       <c r="F16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G16" t="s">
         <v>168</v>
       </c>
       <c r="H16" t="s">
+        <v>263</v>
+      </c>
+      <c r="I16" t="s">
         <v>169</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>170</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>171</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" t="s">
+        <v>247</v>
+      </c>
+      <c r="N16" t="s">
+        <v>258</v>
+      </c>
+      <c r="O16" t="s">
         <v>172</v>
-      </c>
-      <c r="L16" t="s">
-        <v>26</v>
-      </c>
-      <c r="M16" t="s">
-        <v>248</v>
-      </c>
-      <c r="N16" t="s">
-        <v>259</v>
-      </c>
-      <c r="O16" t="s">
-        <v>173</v>
       </c>
       <c r="P16" t="s">
         <v>30</v>
       </c>
       <c r="Q16" t="s">
+        <v>173</v>
+      </c>
+      <c r="R16" t="s">
         <v>174</v>
-      </c>
-      <c r="R16" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>175</v>
+      </c>
+      <c r="B17" t="s">
         <v>176</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>177</v>
       </c>
-      <c r="C17" t="s">
-        <v>178</v>
-      </c>
       <c r="D17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E17" t="s">
         <v>26</v>
@@ -2131,49 +2131,49 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>178</v>
+      </c>
+      <c r="B18" t="s">
         <v>179</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>180</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>180</v>
+      </c>
+      <c r="E18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" t="s">
         <v>181</v>
       </c>
-      <c r="D18" t="s">
-        <v>181</v>
-      </c>
-      <c r="E18" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" t="s">
         <v>182</v>
       </c>
-      <c r="H18" t="s">
-        <v>26</v>
-      </c>
-      <c r="I18" t="s">
-        <v>26</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" t="s">
+        <v>26</v>
+      </c>
+      <c r="N18" t="s">
         <v>183</v>
       </c>
-      <c r="K18" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" t="s">
-        <v>26</v>
-      </c>
-      <c r="M18" t="s">
-        <v>26</v>
-      </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>184</v>
-      </c>
-      <c r="O18" t="s">
-        <v>185</v>
       </c>
       <c r="P18" t="s">
         <v>30</v>
@@ -2187,49 +2187,49 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>185</v>
+      </c>
+      <c r="B19" t="s">
         <v>186</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>187</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>187</v>
+      </c>
+      <c r="E19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" t="s">
         <v>188</v>
       </c>
-      <c r="D19" t="s">
-        <v>188</v>
-      </c>
-      <c r="E19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" t="s">
+        <v>241</v>
+      </c>
+      <c r="K19" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" t="s">
         <v>189</v>
       </c>
-      <c r="H19" t="s">
-        <v>26</v>
-      </c>
-      <c r="I19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J19" t="s">
-        <v>242</v>
-      </c>
-      <c r="K19" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" t="s">
-        <v>26</v>
-      </c>
-      <c r="M19" t="s">
-        <v>26</v>
-      </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>190</v>
-      </c>
-      <c r="O19" t="s">
-        <v>191</v>
       </c>
       <c r="P19" t="s">
         <v>30</v>
@@ -2238,39 +2238,39 @@
         <v>26</v>
       </c>
       <c r="R19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>192</v>
+      </c>
+      <c r="B20" t="s">
         <v>193</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>194</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
+        <v>194</v>
+      </c>
+      <c r="E20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" t="s">
         <v>195</v>
-      </c>
-      <c r="D20" t="s">
-        <v>195</v>
-      </c>
-      <c r="E20" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" t="s">
-        <v>26</v>
-      </c>
-      <c r="I20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J20" t="s">
-        <v>196</v>
       </c>
       <c r="K20" t="s">
         <v>26</v>
@@ -2299,16 +2299,16 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>196</v>
+      </c>
+      <c r="B21" t="s">
         <v>197</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>198</v>
       </c>
-      <c r="C21" t="s">
-        <v>199</v>
-      </c>
       <c r="D21" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E21" t="s">
         <v>26</v>
@@ -2326,7 +2326,7 @@
         <v>26</v>
       </c>
       <c r="J21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K21" t="s">
         <v>26</v>
@@ -2355,16 +2355,16 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>199</v>
+      </c>
+      <c r="B22" t="s">
         <v>200</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>201</v>
       </c>
-      <c r="C22" t="s">
-        <v>202</v>
-      </c>
       <c r="D22" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E22" t="s">
         <v>26</v>
@@ -2382,7 +2382,7 @@
         <v>26</v>
       </c>
       <c r="J22" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K22" t="s">
         <v>26</v>
@@ -2411,85 +2411,85 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>202</v>
+      </c>
+      <c r="B23" t="s">
         <v>203</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>204</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
+        <v>204</v>
+      </c>
+      <c r="E23" t="s">
+        <v>204</v>
+      </c>
+      <c r="F23" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" t="s">
         <v>205</v>
       </c>
-      <c r="D23" t="s">
-        <v>205</v>
-      </c>
-      <c r="E23" t="s">
-        <v>205</v>
-      </c>
-      <c r="F23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>206</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23" t="s">
+        <v>261</v>
+      </c>
+      <c r="L23" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" t="s">
         <v>207</v>
       </c>
-      <c r="I23" t="s">
-        <v>26</v>
-      </c>
-      <c r="J23" t="s">
-        <v>26</v>
-      </c>
-      <c r="K23" t="s">
-        <v>262</v>
-      </c>
-      <c r="L23" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
+        <v>259</v>
+      </c>
+      <c r="O23" t="s">
         <v>208</v>
       </c>
-      <c r="N23" t="s">
-        <v>260</v>
-      </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>26</v>
+      </c>
+      <c r="R23" t="s">
         <v>209</v>
-      </c>
-      <c r="P23" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>26</v>
-      </c>
-      <c r="R23" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>210</v>
+      </c>
+      <c r="B24" t="s">
         <v>211</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>204</v>
+      </c>
+      <c r="D24" t="s">
+        <v>204</v>
+      </c>
+      <c r="E24" t="s">
+        <v>204</v>
+      </c>
+      <c r="F24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" t="s">
         <v>212</v>
       </c>
-      <c r="C24" t="s">
-        <v>205</v>
-      </c>
-      <c r="D24" t="s">
-        <v>205</v>
-      </c>
-      <c r="E24" t="s">
-        <v>205</v>
-      </c>
-      <c r="F24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>213</v>
       </c>
-      <c r="H24" t="s">
-        <v>214</v>
-      </c>
       <c r="I24" t="s">
         <v>26</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>26</v>
       </c>
       <c r="K24" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L24" t="s">
         <v>26</v>
@@ -2506,54 +2506,54 @@
         <v>30</v>
       </c>
       <c r="N24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O24" t="s">
+        <v>214</v>
+      </c>
+      <c r="P24" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>26</v>
+      </c>
+      <c r="R24" t="s">
         <v>215</v>
-      </c>
-      <c r="P24" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>26</v>
-      </c>
-      <c r="R24" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>216</v>
+      </c>
+      <c r="B25" t="s">
         <v>217</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>218</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
+        <v>218</v>
+      </c>
+      <c r="E25" t="s">
+        <v>218</v>
+      </c>
+      <c r="F25" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" t="s">
         <v>219</v>
       </c>
-      <c r="D25" t="s">
-        <v>219</v>
-      </c>
-      <c r="E25" t="s">
-        <v>219</v>
-      </c>
-      <c r="F25" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>220</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J25" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" t="s">
         <v>221</v>
-      </c>
-      <c r="I25" t="s">
-        <v>26</v>
-      </c>
-      <c r="J25" t="s">
-        <v>26</v>
-      </c>
-      <c r="K25" t="s">
-        <v>222</v>
       </c>
       <c r="L25" t="s">
         <v>26</v>
@@ -2562,19 +2562,19 @@
         <v>30</v>
       </c>
       <c r="N25" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O25" t="s">
+        <v>222</v>
+      </c>
+      <c r="P25" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>26</v>
+      </c>
+      <c r="R25" t="s">
         <v>223</v>
-      </c>
-      <c r="P25" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>26</v>
-      </c>
-      <c r="R25" t="s">
-        <v>224</v>
       </c>
     </row>
   </sheetData>
